--- a/Handelshøyskolen/UIA-Handelshøyskolen USE-CASE.xlsx
+++ b/Handelshøyskolen/UIA-Handelshøyskolen USE-CASE.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frank\Desktop\UIA2\Handelshøyskolen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340DD39E-3248-43D9-AC2C-0838ADB234AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DFA998-9E84-40B8-B507-CA6F84E1BDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{42CB6622-B1BC-4A21-A0FB-DBE4D087FF10}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{42CB6622-B1BC-4A21-A0FB-DBE4D087FF10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="577">
   <si>
     <t>Use Case: Seniorrådgiver / Senior Controller ved Handelshøyskolen (HHU) – Universitetet i Agder</t>
   </si>
@@ -3949,6 +3953,4608 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> in Unit4 UBW prior to final board approval to establish an immutable baseline for 2027 variance tracking.</t>
+    </r>
+  </si>
+  <si>
+    <t>Budsjettnotat 2027: Handelshøyskolen ved UiA (HHU)</t>
+  </si>
+  <si>
+    <r>
+      <t>Til:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fakultetsstyret ved Handelshøyskolen ved UiA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fra:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fakultetsadministrasjonen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dato:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 15. oktober 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Saksbehandler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Seniorrådgiver innen strategisk økonomistyring </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gjelder:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Forslag til budsjettramme for 2027</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Executive Summary og Vedtaksforslag</t>
+  </si>
+  <si>
+    <t>Budsjettet for 2027 markerer fullføringen av overgangen til Kunnskapsdepartementets (KD) nye finansieringsregime. For Handelshøyskolen ved UiA (HHU) er dette budsjettet det viktigste verktøyet for å opprettholde faglig autonomi og vår internasjonale posisjon gjennom AACSB-akkrediteringen. Strategien for 2027 er todelt: Vi skal utnytte handlingsrommet i Bevilgningsfinansiert virksomhet (BFV) for å beskytte kjerneaktiviteten, samtidig som vi profesjonaliserer prosjektøkonomien for å sikre vekst gjennom eksternfinansiering (BOA).</t>
+  </si>
+  <si>
+    <t>Hovedmåltallet for 2027 viser et planlagt driftsoverskudd som skal anvendes til strategiske investeringer fremfor passiv sparing:</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Budsjettert 2027 (MNOK)</t>
+  </si>
+  <si>
+    <t>Samlede inntekter</t>
+  </si>
+  <si>
+    <t>286,8</t>
+  </si>
+  <si>
+    <t>Samlede kostnader</t>
+  </si>
+  <si>
+    <t>282,0</t>
+  </si>
+  <si>
+    <t>Forventet driftsresultat</t>
+  </si>
+  <si>
+    <t>+4,8</t>
+  </si>
+  <si>
+    <t>Vedtaksforslag</t>
+  </si>
+  <si>
+    <t>Fakultetsstyret godkjenner budsjettrammen for 2027 med en samlet inntektsramme på 286,8 MNOK og kostnadsramme på 282,0 MNOK.</t>
+  </si>
+  <si>
+    <t>Fakultetsdirektøren gis mandat til å realisere omstillingstiltakene T001–T004 for å sikre budsjettbalanse og faglig handlingsrom.</t>
+  </si>
+  <si>
+    <t>Fakultetsledelsen gis fullmakt til å utarbeide periodiserte investeringsplaner (Capex) for å styre overskuddet i tråd med 5 %-regelen.</t>
+  </si>
+  <si>
+    <t>Budsjettoppfølgingen skal skje i henhold til 3-30-300-regelen med månedlig rapportering av RAG-status i Power BI.</t>
+  </si>
+  <si>
+    <t>Det økonomiske handlingsrommet i 2027 er direkte avhengig av vår evne til å navigere i de nye statlige rammebetingelsene.</t>
+  </si>
+  <si>
+    <t>2. Rammebetingelser og KDs Finansieringsmodell 2027</t>
+  </si>
+  <si>
+    <t>Overgangen til KDs 2025/2027-modell innebærer et skifte mot "styring i det store", der departementet overlater dimensjoneringsrisikoen i sin helhet til fakultetet.</t>
+  </si>
+  <si>
+    <t>Strategisk analyse av finansieringslogikken:</t>
+  </si>
+  <si>
+    <r>
+      <t>Nettobudsjetteringseffekten:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Eksisterende studieplassvolum ligger fast i basisbevilgningen, som fungerer som et beskyttende "skjold" mot devalueringsrisiko. Det er kritisk å forstå at basisbevilgningen dekker våre reelle historiske kostnader, mens nye tildelinger og produksjonsendringer følger de nye satsene.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 1-satser (54 550 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Våre kjernefag innen økonomi, ledelse og juss er plassert i laveste kategori. Denne satsen reflekterer et insentiv for endring, ikke den reelle kostnaden ved utdanning av høy kvalitet. Å skalere opp volum utelukkende basert på denne satsen vil skape et strukturelt underskudd på sikt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-års etterslep på SPE60:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Inntektene i 2027 er låst til produksjonen i 2025. Dette krever at vi i dag styrer gjennomføringsgraden for 3 120 SPE60-ekvivalenter for å sikre inntektsstrømmen i 2029.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konklusjon:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fakultetet må balansere volumvekst strengt mot marginalkostnader, da de nye kategorisatsene undergraver finansieringen av tettere studentoppfølging.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Inntekt- og Kostnadsanalyse (BUD2027 vs. 2026 Baseline)</t>
+  </si>
+  <si>
+    <t>For å sikre sporbarhet og dataintegritet benyttes driverbasert budsjettering, der endringer fra 2026-baseline forklares gjennom aktivitet og lønnsutvikling.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">| Finansiell post | 2026 Baseline (MNOK) | Budsjett 2027 (MNOK) | Endring (%) | | :--- | :--- | : :--- | :--- | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Statlig ramme og BOA-inntekt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | 276,6 | 286,8 | +3,7 % | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lønnskostnader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | 180,9 | 184,0 | +1,7 % | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Drift (inkl. AACSB-avsetning)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | 61,5 | 66,0 | +7,3 % | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Investeringer (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | 32,0 | 32,0 | 0,0 % | | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Netto driftsresultat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+2,2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+4,8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> | </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+118 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> |</t>
+    </r>
+  </si>
+  <si>
+    <t>"So What?"-analyse av lønnsandelen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lønnskostnadene på 184,0 MNOK tilsvarer en lønnsandel på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>64,2 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Dette er under fakultetets kritiske tak på 65 % og gir HHU nødvendig strategisk fleksibilitet.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Strategisk betydning:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> En lønnsandel under 65 % betyr at vi kan absorbere uforutsett prisvekst eller svikt i resultatbevilgningen uten å ty til umiddelbar ansettelsesstopp. Dette handlingsrommet skal brukes til å styrke forskningskapasiteten gjennom målrettede rekrutteringer i tråd med bemanningsplanen.</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Bemanning, Lærertetthet og Omstillingstiltak</t>
+  </si>
+  <si>
+    <t>Årsverksstyring er vårt kraftigste verktøy for økonomisk bærekraft. Bemanningsplanen for 2027 er dimensjonert for å håndtere 3 450 registrerte studenter med høy faglig kvalitet.</t>
+  </si>
+  <si>
+    <t>Nøkkeltall for bemanning:</t>
+  </si>
+  <si>
+    <r>
+      <t>Totalt 230 årsverk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 155 UF (vitenskapelige) og 75 TA (teknisk-administrative).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lærertetthet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 22,3 studenter per UF-årsverk. Dette er en sunn ratio som underbygger kravene i AACSB-akkrediteringen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansfaktor:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Det er lagt inn en sentral vakansreduksjon på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3–5 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> i budsjettet. Dette er et proaktivt grep for å unngå overbudsjettering av lønn grunnet naturlig rekrutteringstid.</t>
+    </r>
+  </si>
+  <si>
+    <t>Omstillingstiltak (T001–T004):</t>
+  </si>
+  <si>
+    <t>For å eliminere restavvik og styrke driftsmarginen skal fakultetet:</t>
+  </si>
+  <si>
+    <r>
+      <t>Sanere</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ulønnsomme emner med lav studenttilstrømning gjennom en kritisk porteføljeanalyse.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Optimalisere</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> studieporteføljen for å øke SPE60-produksjonen per UF-årsverk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stramme inn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> på administrative støtteprosesser ved å utnytte fellestjenester i større grad. Disse tiltakene overvåkes i </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FactAction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-tabellen for å sikre at realiseringsgraden korresponderer med budsjettmålene.</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Forskning, BOA-prosjektøkonomi og AACSB</t>
+  </si>
+  <si>
+    <t>HHU må balansere kravet til AACSB-akkreditering mot fraværet av nasjonale publiseringsinsentiver. Løsningen er en offensiv satsing på eksternfinansiering.</t>
+  </si>
+  <si>
+    <t>Strategiske suksessfaktorer:</t>
+  </si>
+  <si>
+    <r>
+      <t>TDI-modellen og overhead:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Vi benytter et påslag for indirekte kostnader (overhead) på ca. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>22 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Det er en strategisk balansegang: For høy overhead svekker våre forskeres konkurransekraft i NFR/EU-søknader, mens for lav dekningsgrad fører til at BFV-midler subsidierer eksterne oppdragsgivere.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Frikjøp (Buy-out):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Aktiv bruk av frikjøp er obligatorisk for å flytte lønnskostnader fra basisbudsjettet og skape rom for nye rekrutteringsstillinger.</t>
+    </r>
+  </si>
+  <si>
+    <t>Regnskapsmessig risiko (SRS 9 vs. SRS 10):</t>
+  </si>
+  <si>
+    <r>
+      <t>SRS 10 (Bidrag):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Inntektsføres i takt med kostnader (motsatt sammenstilling).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SRS 9 (Oppdrag/EVU):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Her ligger den største risikoen. Eventuelle underskudd i oppdragsprosjekter utløser krav om umiddelbar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>avsetning for forventet tap (Konto 7790/2800)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Dette vil direkte belaste overskuddet på 4,8 MNOK og må unngås gjennom tett prosjektcontrolling.</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Risikovurdering, 5 %-regelen og Digital Oppfølging</t>
+  </si>
+  <si>
+    <t>Controllerens rolle er å fungere som strategisk navigatør gjennom Power BI-dashbordet, der vi beveger oss fra data til handling.</t>
+  </si>
+  <si>
+    <t>Kritiske kontrollpunkter:</t>
+  </si>
+  <si>
+    <r>
+      <t>5 %-regelen (F-05-20) som planleggingsverktøy:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Et overskudd på 4,8 MNOK utgjør en risiko for inndragning dersom det ikke er knyttet til forpliktelser. Vi skal bruke 5 %-regelen som et "skjold" ved å etablere </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>flerårige investeringsplaner (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Dette forhindrer "desember-panikk" og sikrer at midlene investeres i lab-infrastruktur og digital omstilling fremfor kortsiktige utstyrskjøp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Power BI &amp; 3-30-300-regelen:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Ledelsen skal overvåke budsjettavvik via dashbordet:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Grønn (&lt;= 2 %):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Planmessig drift.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Gul (2-5 %):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Krever observasjon og interne justeringer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Rød (&gt; 5 %):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Kritisk avvik som krever skriftlig rapport og umiddelbare tiltak i </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FactAction</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Langsiktige utsikter 2027–2031:</t>
+  </si>
+  <si>
+    <r>
+      <t>Dimensjoneringsrisiko:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Kontinuerlig vurdering av studieporteføljen opp mot de lave kategorisatsene.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Økonomisk bærekraft:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Det positive resultatet i 2027 er en nødvendig buffer for fremtidige svingninger i KDs resultatbevilgning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BOA-vekst:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Økt eksternfinansiering er den eneste veien til betydelig kapasitetsøkning i forskning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Oppsummering:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Budsjett 2027 ruster Handelshøyskolen ved UiA for fremtiden. Ved å kombinere streng kostnadskontroll med offensive investeringer og profesjonalisert prosjektøkonomi, sikrer vi HHUs posisjon som et autonomt og internasjonalt anerkjent fakultet.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I offentlig sektor og universitets- og høgskolesektoren (UH) har budsjettering beveget seg fra passiv historisk rammetildeling til strategisk virksomhetsstyring. Nedenfor gis en gjennomgang av de mest sentrale budsjetteringsmetodene, følges opp av en konkret anbefaling for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Handelshøyskolen ved UiA (HHU)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Oversikt over ulike budsjetteringsmetoder</t>
+  </si>
+  <si>
+    <t>A. Historisk / Inkrementell budsjettering (Rammebudsjettering)</t>
+  </si>
+  <si>
+    <t>B. Driverbasert budsjettering (Driver-Based Budgeting)</t>
+  </si>
+  <si>
+    <t>C. Totalkostnadsbudsjettering (TDI-modellen for BOA)</t>
+  </si>
+  <si>
+    <t>D. Rullende prognoser (Rolling Forecast / Latest Estimate – LE)</t>
+  </si>
+  <si>
+    <t>E. Nullbasert budsjettering (Zero-Based Budgeting – ZBB)</t>
+  </si>
+  <si>
+    <t>2. Anbefalt budsjettmodell for HHU</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Handelshøyskolen ved UiA (HHU)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> anbefales en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>hybrid modell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> som kombinerer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Driverbasert budsjettering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TDI-modellen for BOA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> og </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rullende prognoser (LE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Modelldesignet må tilpasses de spesifikke rammebetingelsene som gjelder for fakultetet:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   [ DRIVERBASET BEMANNING ]     Årsverksstyring i UBW (UF/TA, vakansfaktor 3-5%, ansettelsestid)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              ▼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   [ KD 2025 VOLUMMODELL ]       SPE60-produksjon x Kat. 1 (54 550 kr) m/ 2-års etterslep &amp; nettobudsjettering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   [ TDI &amp; FRIKJØP (BOA) ]       Prosjektfrikjøp overfører lønn fra basis til NFR/EU m/ overhead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   [ LE &amp; RULLENDE PROGNOSE ]    Oppfølging T1/T2/T3 i Power BI mot 5 %-regelen (F-05-20)</t>
+  </si>
+  <si>
+    <t>Hvorfor denne modellen er optimal for HHU:</t>
+  </si>
+  <si>
+    <t>Presis styring av lønnskostnader (Driverbasert bemanningsplanlegging):</t>
+  </si>
+  <si>
+    <t>Lønn utgjør ca. 65–71 % av totalkostnadene ved UiA og HHU.</t>
+  </si>
+  <si>
+    <t>Håndtering av KDs 2025-modell og lærertetthet:</t>
+  </si>
+  <si>
+    <t>Kontinuerlig risikostyring og 5 %-regelen (F-05-20):</t>
+  </si>
+  <si>
+    <t>Oppsummering for Senior Controller ved HHU</t>
+  </si>
+  <si>
+    <t>Anbefalt Metode</t>
+  </si>
+  <si>
+    <t>Hovedfokus / Styringssignal</t>
+  </si>
+  <si>
+    <t>Lønn &amp; Bemanning</t>
+  </si>
+  <si>
+    <t>Driverbasert (UBW Planlegger)</t>
+  </si>
+  <si>
+    <t>Stillingsgrupper, sosiale kostnader, 3–5 % vakansfaktor, 3–6 mnd rekrutteringstid.</t>
+  </si>
+  <si>
+    <t>Utdanningsinntekter</t>
+  </si>
+  <si>
+    <t>Driverbasert (KD 2025-modell)</t>
+  </si>
+  <si>
+    <t>SPE60-produksjon, 2-års etterslep, Kategori 1 (54 550 kr) og nettobudsjettering.</t>
+  </si>
+  <si>
+    <t>Ekstern Forskning (BOA)</t>
+  </si>
+  <si>
+    <t>TDI-modellen</t>
+  </si>
+  <si>
+    <r>
+      <t>Frikjøpsbalanse (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), korrekt SRS 10-periodisering og full overhead-dekning.</t>
+    </r>
+  </si>
+  <si>
+    <t>Løpende Oppfølging</t>
+  </si>
+  <si>
+    <t>Rullende prognoser (LE) &amp; Power BI</t>
+  </si>
+  <si>
+    <t>T3 Cutoff, avviksdrivere, RAG-status og overvåking mot 5 %-regelen (F-05-20).</t>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fjorårets budsjett eller regnskap legges til grunn som baseline, og justeres marginalt opp eller ned basert på generell pris- og lønnsvekst (deflator) samt flate rammekutt (f.eks. ABE-kutt).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Enkel å gjennomføre, krever lite ressursbruk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Konserverer historiske skjevheter, skjermer ineffektive aktiviteter og fanger i liten grad opp reelle endringer i studieproduksjon eller bemanningsstruktur.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Budsjettet bygges opp fra underliggende operasjonelle volum- og aktivitetsdrivere.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Inntektssiden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> styres av KDs finansieringsmodell (antall avlagte studiepoeng/SPE60, kandidater og PhD-er).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kostnadssiden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> styres av antall årsverk (UF/TA), lønnstrinn, sosiale kostnader, antall emner og undervisningstimer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Høy presisjon, direkte kobling mellom faglig aktivitet og økonomisk konsekvens, og mulighet for årsakssammenhengende avviksanalyser (volum- vs. prisavvik).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Krever god datakvalitet på tvers av fagsystemer (Unit4 ERP, SAP Lønn, FS).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Benyttes spesifikt for eksternfinansiert forskning og oppdrag (Bidrags- og oppdragsaktivitet / BOA). Beregner alle direkte prosjektkostnader (lønn, reiser, drift) pluss et standardisert påslag for indirekte felleskostnader (overhead for husleie, IT, bibliotek og administrasjon – typisk ~22 %).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Sikrer at eksterne prosjekter ikke underfinansieres eller subsidieres ulovlig av grunnbevilgningen, samt synliggjør verdien av frikjøp (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> I stedet for å behandle årsbudsjettet som en låst, statisk størrelse gjennom regnskapsåret, oppdateres forventet årsresultat (Latest Estimate / EAC) kontinuerlig ved tertialene (T1/T2/T3) ved å kombinere bokført regnskap (Actuals YTD) med oppdaterte estimater for resten av året (ETC).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Gjøre ledelsen i stand til å fange opp avvik tidlig og iverksette korrigerende tiltak før året er omme.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hver enhet må begrunne alle sine kostnader fra «null» ved hver nye budsjettrunde, uavhengig av historisk nivå.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Identifiserer uhensiktsmessig ressursbruk og tvinger frem streng prioritering.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Svært krevende og lite egnet for UH-sektoren som helhet, ettersom faste lønnskostnader og studieprogrammer ligger fast på lang sikt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bemanningsbudsjettet i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Unit4 UBW Planlegger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> må bygges opp driverbasert på individ- og stillingsgruppenivå (Professorer, Førsteamanuenser, Stipendiater, TA-ansatte).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansestyring:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Det </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>må</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> legges inn en innlagt central vakansfaktor (3–5 %) og realistisk rekrutteringstid (3–6 måneder) for å unngå systematisk overbudsjettering av fast lønn.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HHUs studier (økonomi, ledelse, juss) tilhører KDs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Kategori 1 (54 550 kr per 60 SPE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2-års etterslep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> på resultatbevilgningen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HHU har en lærertetthet på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>22,3 studenter per UF-årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nettobudsjetteringsprinsippet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ligger eksisterende volum fast i basisbevilgningen, mens volumendringer utløser Kategori 1-satser. Fordi Kategori 1-satsen er lav, må den driverbaserte inntektsmodellen vise at ubegrenset studentvekst uten tilsvarende bevilgningsøkning i praksis kan svekke fakultetets marginer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Aktiv bruk av TDI-modellen for frikjøp (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For å opprettholde høyt forskningstrykk og finansiere rekrutteringsstillinger (PhD/Postdok) – som er avgjørende for HHUs internasjonale </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AACSB-akkreditering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> – må prosjektøkonomien budsjetteres etter TDI-modellen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ved å budsjettere vitenskapelige ansattes tid inn i NFR- og EU-prosjekter (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>frikjøp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>), overføres lønnskostnader fra basisbudsjettet til ekstern finansiering, samtidig som fakultetet sikres full overhead-dekning (~22 %) til fellesinfrastruktur.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ved å kombinere vedtatt årsbudsjett (BUD) med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rullende prognoser (LE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ved T1, T2 og T3, kan controlleren og fakultetsledelsen fange opp avvik tidlig.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dette forhindrer «desember-panikk» og sikrer at akkumulerte ubrukte midler avsettes til godkjente flerårige investeringsplaner (f.eks. IT, lab, AACSB-evalueringer) i tråd med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5 %-regelen (F-05-20)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I offentlig sektor og universitets- og høgskolesektoren (UH) har budsjettering beveget seg fra passiv historisk rammetildeling til strategisk virksomhetsstyring12. Nedenfor gis en gjennomgang av de mest sentrale budsjetteringsmetodene, følges opp av en konkret anbefaling for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Handelshøyskolen ved UiA (HHU)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Fjorårets budsjett eller regnskap legges til grunn som baseline, og justeres marginalt opp eller ned basert på generell pris- og lønnsvekst (deflator) samt flate rammekutt (f.eks. ABE-kutt)12.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Enkel å gjennomføre, krever lite ressursbruk.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Konserverer historiske skjevheter, skjermer ineffektive aktiviteter og fanger i liten grad opp reelle endringer i studieproduksjon eller bemanningsstruktur12.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Budsjettet bygges opp fra underliggende operasjonelle volum- og aktivitetsdrivere23.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Inntektssiden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> styres av KDs finansieringsmodell (antall avlagte studiepoeng/SPE60, kandidater og PhD-er)23.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kostnadssiden</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> styres av antall årsverk (UF/TA), lønnstrinn, sosiale kostnader, antall emner og undervisningstimer34.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Høy presisjon, direkte kobling mellom faglig aktivitet og økonomisk konsekvens, og mulighet for årsakssammenhengende avviksanalyser (volum- vs. prisavvik)45.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Krever god datakvalitet på tvers av fagsystemer (Unit4 ERP, SAP Lønn, FS)46.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Benyttes spesifikt for eksternfinansiert forskning og oppdrag (Bidrags- og oppdragsaktivitet / BOA)3more_horiz. Beregner alle direkte prosjektkostnader (lønn, reiser, drift) pluss et standardisert påslag for indirekte felleskostnader (overhead for husleie, IT, bibliotek og administrasjon – typisk ~22 %)3more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sikrer at eksterne prosjekter ikke underfinansieres eller subsidieres ulovlig av grunnbevilgningen, samt synliggjør verdien av frikjøp (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)47.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> I stedet for å behandle årsbudsjettet som en låst, statisk størrelse gjennom regnskapsåret, oppdateres forventet årsresultat (Latest Estimate / EAC) kontinuerlig ved tertialene (T1/T2/T3) ved å kombinere bokført regnskap (Actuals YTD) med oppdaterte estimater for resten av året (ETC)4more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Gjøre ledelsen i stand til å fange opp avvik tidlig og iverksette korrigerende tiltak før året er omme4more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Konsept:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Hver enhet må begrunne alle sine kostnader fra «null» ved hver nye budsjettrunde, uavhengig av historisk nivå.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fordeler:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Identifiserer uhensiktsmessig ressursbruk og tvinger frem streng prioritering.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ulemper:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Svært krevende og lite egnet for UH-sektoren som helhet, ettersom faste lønnskostnader og studieprogrammer ligger fast på lang sikt1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Handelshøyskolen ved UiA (HHU)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> anbefales en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hybrid modell</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> som kombinerer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Driverbasert budsjettering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TDI-modellen for BOA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> og </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rullende prognoser (LE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3more_horiz. Modelldesignet må tilpasses de spesifikke rammebetingelsene som gjelder for fakultetet:</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Presis styring av lønnskostnader (Driverbasert bemanningsplanlegging):</t>
+  </si>
+  <si>
+    <t>Lønn utgjør ca. 65–71 % av totalkostnadene ved UiA og HHU4more_horiz.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bemanningsbudsjettet i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unit4 UBW Planlegger</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> må bygges opp driverbasert på individ- og stillingsgruppenivå (Professorer, Førsteamanuenser, Stipendiater, TA-ansatte)413.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansestyring:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Det </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>må</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> legges inn en innlagt central vakansfaktor (3–5 %) og realistisk rekrutteringstid (3–6 måneder) for å unngå systematisk overbudsjettering av fast lønn34.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Håndtering av KDs 2025-modell og lærertetthet:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HHUs studier (økonomi, ledelse, juss) tilhører KDs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kategori 1 (54 550 kr per 60 SPE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2-års etterslep</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> på resultatbevilgningen2more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HHU har en lærertetthet på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>22,3 studenter per UF-årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1516.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nettobudsjetteringsprinsippet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ligger eksisterende volum fast i basisbevilgningen, mens volumendringer utløser Kategori 1-satser2more_horiz. Fordi Kategori 1-satsen er lav, må den driverbaserte inntektsmodellen vise at ubegrenset studentvekst uten tilsvarende bevilgningsøkning i praksis kan svekke fakultetets marginer2more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Aktiv bruk av TDI-modellen for frikjøp (Buy-out):</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">For å opprettholde høyt forskningstrykk og finansiere rekrutteringsstillinger (PhD/Postdok) – som er avgjørende for HHUs internasjonale </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AACSB-akkreditering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> – må prosjektøkonomien budsjetteres etter TDI-modellen4more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ved å budsjettere vitenskapelige ansattes tid inn i NFR- og EU-prosjekter (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>frikjøp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), overføres lønnskostnader fra basisbudsjettet til ekstern finansiering, samtidig som fakultetet sikres full overhead-dekning (~22 %) til fellesinfrastruktur3more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Kontinuerlig risikostyring og 5 %-regelen (F-05-20):</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ved å kombinere vedtatt årsbudsjett (BUD) med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rullende prognoser (LE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ved T1, T2 og T3, kan controlleren og fakultetsledelsen fange opp avvik tidlig4more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dette forhindrer «desember-panikk» og sikrer at akkumulerte ubrukte midler avsettes til godkjente flerårige investeringsplaner (f.eks. IT, lab, AACSB-evalueringer) i tråd med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5 %-regelen (F-05-20)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>Stillingsgrupper, sosiale kostnader, 3–5 % vakansfaktor, 3–6 mnd rekrutteringstid34.</t>
+  </si>
+  <si>
+    <t>SPE60-produksjon, 2-års etterslep, Kategori 1 (54 550 kr) og nettobudsjettering2more_horiz.</t>
+  </si>
+  <si>
+    <r>
+      <t>Frikjøpsbalanse (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), korrekt SRS 10-periodisering og full overhead-dekning4more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>T3 Cutoff, avviksdrivere, RAG-status og overvåking mot 5 %-regelen (F-05-20)4more_horiz.</t>
+  </si>
+  <si>
+    <t>keep_pinSave to notekeep_pin</t>
+  </si>
+  <si>
+    <t>copy</t>
+  </si>
+  <si>
+    <t>thumb_up</t>
+  </si>
+  <si>
+    <t>thumb_down</t>
+  </si>
+  <si>
+    <t>Forklar 2025-finansieringsmodellen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thoughts </t>
+  </si>
+  <si>
+    <t>expand_more</t>
+  </si>
+  <si>
+    <r>
+      <t>Kunnskapsdepartementets (KD) finansieringsmodell fra 2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> innebærer en forenkling og omlegging av statens tildelingssystem for universiteter og høyskoler12. Modellen flytter tyngdepunktet mot en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>styrket basisbevilgning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> kombinert med en </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rendyrket åpen resultatramme</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> knyttet til utdanningsproduksjon1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Hovedkomponentene i 2025-modellen</t>
+  </si>
+  <si>
+    <t>1. Styrket basisbevilgning (Avvikling av lukkede resultatrammer):</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tidligere «lukkede resultatindikatorer» for forskningspublisering (publiseringspoeng), inntekter fra Norges forskningsråd (NFR), EU (Horisont Europa) og øvrig bidrags- og oppdragsaktivitet (BOA) er </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>avviklet som egne løpende resultatindikatorer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> i den nasjonale modellen12.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Disse resultatmidlene er i stedet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>innlemmet i den faste basisbevilgningen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> basert på et treårig historisk gjennomsnitt (2020–2022)12. Dette gir økt forutsigbarhet, men innebærer også at den automatiske statlige «skurtresker-effekten» for nye publiseringspoeng faller bort13.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Åpen resultatbasert ramme (Utdanningsproduksjon):</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Antall resultatbaserte kategorier for studiepoengutveksling/produksjon er redusert fra tidligere seks kategorier (A–F) til </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tre kategorier</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 1 (54 550 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Humaniora, samfunnsfag og økonomisk-administrative fag (f.eks. studiene ved Handelshøyskolen ved UiA)1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 2 (81 800 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Realfag, helse-, sosial- og lærerutdanninger, samt profesjonsstudiet i psykologi1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 3 (190 900 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Medisin, odontologi og veterinærmedisin1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Sentrale mekanismer og kontrollpunkter</t>
+  </si>
+  <si>
+    <r>
+      <t>Nettobudsjetteringsprinsippet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Eksisterende studieplasser og historisk produksjonsvolum ligger i utgangspunktet fast beskyttet i basisbevilgningen1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Marginale endringer:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Kategorisatsene (f.eks. 54 550 kr for Kategori 1) benyttes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kun ved endringer i produksjonsvolum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (vekst eller fall i avlagte studiepoeng) eller ved tildeling av nye studieplasser1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-års etterslep (lag):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resultatbasert uttelling for avlagte studiepoeng (SPE60) utbetales med to års etterslep (f.eks. vil studiepoeng produsert i 2025 gi utslag i resultatbevilgningen for 2027)5.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Skille i satser ved tildeling:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ved tildeling av </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>helt nye</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> studieplasser benyttes en overordnet standardsats (ca. 100 100 kr, fordelt med ca. 60 % i basis og 40 % resultatbasert), mens kategorisatsene benyttes for rene produksjonsendringer i eksisterende masse4.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Strategiske konsekvenser for Controlleren</t>
+  </si>
+  <si>
+    <r>
+      <t>Kritisk advarsel mot feilbruk av satser:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> KDs kategorisatser uttrykker statlige </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>insentivmidler per studiepoeng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ikke institusjonens faktiske kostnader ved å drive utdanningen2more_horiz. Hvis en enhet feilaktig benytter de lave marginale kategorisatsene som grunnlag for å omfordele eller devaluere eksisterende historisk studievolum internt, vil det undervurdere de reelle kostnadene og undergrave enhetens økonomiske bærekraft2more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Økt institusjonell forskningsrisiko:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Fordi statlig uttelling for publisering og BOA-prosjekter nå ligger fast i basis, flyttes den økonomiske risikoen for forskningsaktivitet i sin helhet over på institusjonen13. Frikjøp (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>buy-out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) over eksterne NFR/EU-prosjekter via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TDI-modellen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> blir dermed enda viktigere for å avlaste basisbevilgningen og fristille forskningstid13.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">💡 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ønsker du at jeg viser et regneeksempel på hvordan en volumendring i studiepoeng slår ut på tildelingen for et konkret fakultet (f.eks. HHU eller TEK)?</t>
+    </r>
+  </si>
+  <si>
+    <t>Vis et regneeksempel på Kat 1 volumendring</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Her er et praktisk regneeksempel på hvordan en volumendring i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kategori 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> slår ut under Kunnskapsdepartementets (KDs) finansieringsmodell12.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Grunnleggende forutsetninger for Kategori 1</t>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 1-sats:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>54 550 kr per 60 studiepoeng (1 SPE60 / helårsstudent)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (gjelder fag innen humaniora, samfunnsfag og økonomisk-administrative fag, som Handelshøyskolen ved UiA)12.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-års etterslep (lag):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Studiepoeng produsert i regnskapsåret </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> utløser resultatutbetaling i statsbudsjettet for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nettobudsjetteringsprinsippet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Eksisterende historisk studievolum ligger fast beskyttet i universitetets </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>basisbevilgning</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1more_horiz. Kategorisatsen på 54 550 kr benyttes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kun på marginale endringer i volum</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Økning eller reduksjon i avlagte studiepoeng)1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Regneeksempel: Volumendring ved Handelshøyskolen (HHU)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Anta at Handelshøyskolen ved UiA har en historisk baseline i sin basisbevilgning på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3 120 SPE60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tilsvarende 187 200 avlagte studiepoeng)14.</t>
+    </r>
+  </si>
+  <si>
+    <t>Scenario A: Positive volumendring (+50 SPE60 i 2025)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gjennom tiltak for bedre gjennomføring og redusert stryk øker studentenes produksjon i 2025 med totalt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3 000 studiepoeng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, som utgjør </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+50 SPE60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ($3\,000 / 60 = 50$).</t>
+    </r>
+  </si>
+  <si>
+    <t>$$\text{Marginal inntektsendring for 2027} = 50 \text{ SPE60} \times 54\,550 \text{ kr} = \mathbf{2\,727\,500 \text{ kr}} \quad (\mathbf{+2,73 \text{ MNOK}})$$</t>
+  </si>
+  <si>
+    <r>
+      <t>Effekt i 2027-budsjettet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> HHU får utbetalt en resultatvekst i bevilgningen fra KD på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+2,73 MNOK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> i 202712.</t>
+    </r>
+  </si>
+  <si>
+    <t>Scenario B: Negativ volumendring (-30 SPE60 i 2025)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">På grunn av økt frafall på et bachelorprogram faller produksjonen i 2025 med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 800 studiepoeng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, som utgjør </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-30 SPE60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ($1\,800 / 60 = 30$).</t>
+    </r>
+  </si>
+  <si>
+    <t>$$\text{Marginal inntektsendring for 2027} = -30 \text{ SPE60} \times 54\,550 \text{ kr} = \mathbf{-1\,636\,500 \text{ kr}} \quad (\mathbf{-1,64 \text{ MNOK}})$$</t>
+  </si>
+  <si>
+    <r>
+      <t>Effekt i 2027-budsjettet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> HHU får et trekk i resultatbevilgningen fra KD på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-1,64 MNOK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> i 202712.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Controllerens «So What?» &amp; Strategiske Advarsler</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Insentivsats vs. Reell enhetskostnad:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> KDs kategorisats på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>54 550 kr per SPE60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> uttrykker kun statens </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>marginalbelønning for endring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ikke den faktiske totalkostnaden ved å utdanne en helårsstudent (som inkluderer lønn til forelesere, lokaler, IT og administrasjon)1more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. Kritisk kontrollpunkt mot devaluering:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Som controller må du </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>aldri</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> benytte 54 550 kr som grunnlag for å verdivurdere hele den eksisterende studentmassen ($3\,120 \text{ SPE60} \times 54\,550 \text{ kr} = 170,2 \text{ MNOK}$) når midler fordeles internt2more_horiz. Det historiske volumet er finansiert over basis, og feilaktig bruk av kategorisatsen på eksisterende volum vil undervurdere de reelle kostnadene og undergrave fakultetets økonomiske bærekraft2more_horiz.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. Tidsforskyvning og treghet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Et produksjonsfall i 2025 gir ikke umiddelbar regnskapseffekt i 2025 eller 2026, men skaper et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>forsinket bevilgningshull i 2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2more_horiz. Controlleren må derfor advare ledelsen om denne effekten to år før regningen faktisk kommer34.</t>
+    </r>
+  </si>
+  <si>
+    <t>Oversikt over genererte CSV-filer for Budsjett 2027</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Settet med </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9 CSV-filer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> er bygget med semi-kolon (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) som skilletegn og UTF-8 med BOM for direkte import i Power BI Desktop:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. FactBudget_2027.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Detaljert månedsperiodisert årsbudsjett (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BUD2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) for alle 12 måneder i 2027 fordelt på kontoplan R-102 og organisasjonsenheter. Reflekterer HHUs samlede ramme på </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>286,8 MNOK i inntekter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> og </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>282,0 MNOK i kostnader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (+4,8 MNOK i netto overskudd) samt UiAs totalramme (ca. 1 500 MNOK).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. FactFTE_2027.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Bemannings- og årsverksplan for 2027. For HHU inngår </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>155 UF-årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (vitenskapelige), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>75 TA-årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (teknisk-administrative), totalt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>230 årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (252 ansatte), med innlagt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3–5 % vakansfaktor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> og snittlønnsdata.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. FactStudents_2027.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Utdannings- og studiepoengmodell for 2027. Dokumenterer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2-års etterslep (lag)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> der </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025-produksjonen (3 120 SPE60)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> styrer resultatutbetalingen i 2027 basert på KDs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kategori 1-sats (54 550 kr/SPE60)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for HHU, samt lærertetthet (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>22,3 stud/UF-ÅV</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4. FactAction_2027.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Omstillingstiltak T001–T004 for 2027 (frys i administrativ rekruttering, faglige omdisponeringer, EVU-ekspansjon) koblet mot regnskapslinjer og ansvarlige roller.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5. DimOrganization.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: UiA organisasjonsstruktur (Toppnivå UiA, HHU og øvrige fakulteter, samt HHUs tre institutter og fakultetsadministrasjon).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6. DimAccountHierarchy.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Denormalisert kontoplan iht. DFØ R-102 og SRS-regnskapslinjer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. DimDate_2027.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kalenderdimensjon for 2027 som markerer hele året som plan/budsjettperiode (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ErActualYTD = FALSE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8. DimForecastVersion.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Versjonstabell (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>BUD2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PROG2028</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PROG2029</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PROG2030</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>PROG2031</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9. Relationships.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Kardinalitets- og kryssfiltreringstabell ($1:*$ enveisrelasjoner) for oppsett av datamodellen.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. Data Model Diagram (Power BI Star Schema 2027)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bildet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>powerbi_datamodel_2027_diagram.png</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> viser oppsettet av semantikkmodellen i Power BI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Datamodellen er bygget som et </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renskåret Stjerneskjema (Star Schema)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hvor dimensjonstabellene filtrerer faktatabellene med enveis $1:*$-relasjoner:</t>
+    </r>
+  </si>
+  <si>
+    <t>| POWER BI SEMANTIC DATA MODEL — UiA &amp; HHU BUDSJETT 2027 (STAR SCHEMA)                             |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    [ DimOrganization ]        [ DimAccountHierarchy ]        [ DimDate_2027 ]      [ DimForecastVersion ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     (PK: OrgKode)              (PK: Konto)                (PK: DatoNokkel)       (PK: VersjonKode)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           │                          │                           │                      │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           │ (1)                      │ (1)                       │ (1)                  │ (1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           ├──────────────────────────┼───────────────────────────┼──────────────────────┘</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           │                          │                           │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           ▼ (*)                      ▼ (*)                       ▼ (*)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  +───────────────────+      +───────────────────+       +───────────────────+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  |  FactBudget_2027  |      |   FactFTE_2027    |       | FactStudents_2027 |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  | (FK: OrgKode)     |      | (FK: OrgKode)     |       | (FK: OrgKode)     |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  | (FK: Konto)       |      | (FK: DatoNokkel)  |       | [SPE60_2025_Lag,  |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  | (FK: DatoNokkel)  |      | [UF/TA, ÅV, Lønn] |       |  Kat 1 54 550 kr] |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           │                                                       │</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           ▼ (*)                                                   ▼ (*)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  +───────────────────+                                  +───────────────────+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  |   FactAction_2027 |                                  | Relationships.csv |</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  | (FK: OrgKode)     |                                  | (Relasjonskart)   |</t>
+  </si>
+  <si>
+    <t>3. Ordliste for Økonomi, Finansiering og Budsjett (HHU &amp; UiA)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dokumentet </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ordliste_HHU_UIA_Oekonomi_Budsjett_2027.md</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> er publisert i Studio. Nedenfor gies sammendraget av kjjernebegrepene:</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Sektor- og Finansieringsbegreper</t>
+  </si>
+  <si>
+    <r>
+      <t>KD (Kunnskapsdepartementet):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Overordnet sektordepartement som tildeler statstilskuddet via det årlige tildelingsbrevet (Kap. 260).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BFV (Bevilgningsfinansiert virksomhet):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ordinær kjernevirksomhet finansiert over statsbudsjettets Post 50 basisbevilgning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BOA (Bidrags- og oppdragsfinansiert aktivitet):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Eksternfinansiert forskning og utdanning.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bidrag (NFR, EU Horisont Europa):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Støtte uten krav om kommersiell motytelse (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SRS 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> periodisering).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Oppdrag (EVU, næringsliv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Salg av tjenester mot betaling (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SRS 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fullføringsgrad og tapsavsetning).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TDI-modellen:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nasjonal UH-standard for beregning av direkte prosjektkostnader pluss et felleskostnadspåslag (overhead på ca. 22 %).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Frikjøp (Buy-out):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Overføring av vitenskapelig ansattes lønnskostnad fra basisbudsjettet til BOA-prosjekter.</t>
+    </r>
+  </si>
+  <si>
+    <t>2. KDs Finansieringsmodell 2025/2027 &amp; Kategoriinndeling</t>
+  </si>
+  <si>
+    <r>
+      <t>Nettobudsjetteringsprinsippet:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Eksisterende utdanningsvolum ligger fast beskyttet i basisbevilgningen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 1 (54 550 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Humaniora, samfunnsfag og økonomisk-administrative fag (HHU).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 2 (81 800 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Realfag, helse-, sosial- og lærerutdanninger, psykologi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Kategori 3 (190 900 kr per 60 SPE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Medisin, odontologi og veterinærmedisin.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-Års Etterslep (Lag):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Studiepoeng avlagt i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gir resultatbetaling på statsbudsjettet i </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Budsjetteringsmetoder &amp; Prosess</t>
+  </si>
+  <si>
+    <r>
+      <t>BUD2027:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vedtatt årsbudsjettbaseline for 2027.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BAC (Budget at Completion):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Samlet godkjent budsjettramme ved årets start.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EAC (Estimate at Completion / Latest Estimate - LE):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Oppdatert helårsprognose.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Driverbasert Budsjettering:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Budsjettmetode basert på operasjonelle volumdrivere (årsverk, stillingsgrupper, SPE60, studenter) i Unit4 UBW Planlegger.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Systemfrys (Freeze):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Låsing av budsjettgrunnlaget i UBW for uforanderlig audit-trail.</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Bemannings- og Kapasitetsstyring</t>
+  </si>
+  <si>
+    <r>
+      <t>FTE / Årsverk:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Måleenhet for arbeidskraft (1,0 årsverk = 1950 timer). HHU har </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>230 årsverk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>155 UF / 75 TA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lønnsandel %:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Personalkostnadenes andel av totale driftskostnader (HHU target: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>64,2 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, sektornorm: 62–65 %).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansfaktor:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Innlagt reduksjon i lønnsbudsjettet (3–5 %) for å ta høyde for avgang og rekrutteringstid (3–6 måneder).</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Regnskapsstandarder &amp; Lovverk (SRS &amp; DFØ)</t>
+  </si>
+  <si>
+    <r>
+      <t>SRS 9:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Salgs- og oppdragsinntekter (fullføringsgrad og tapsavsetning på konto 7790).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SRS 10:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Inntektsføring av bidrag i takt med medgåtte prosjektkostnader.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SRS 17:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Aktivering og avskrivning av IKT og utstyr over 50 000 kr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F-05-20 (5 %-regelen):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Krav om at ubrukte bevilgningsmidler (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>formålskapital</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) over 5 % må være formelt avsatt til godkjente investeringsplaner for å unngå inndragning.</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Power BI &amp; Visualisering</t>
+  </si>
+  <si>
+    <r>
+      <t>3-30-300-regelen:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Informasjonshierarki (3 sekunder KPI-kort, 30 sekunder trend/stolpediagram, 300 sekunder granulær matrise).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>RAG-status:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trafikklysklassifisering (🟢 Grønn = I budsjett, 🟡 Gul = 2–5 % avvik, 🔴 Rød = &gt; 5 % avvik).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I statlig økonomistyring og ved Universiteter og høyskoler (UiA) brukes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>vakans</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> og relaterte begreper om ubesatte stillinger og hvordan disse styres i bemannings- og lønnsbudsjettet:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">💡 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sluttsum for controlleren:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Lønn utgjør over </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>65–70 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> av universitetets kostnader, så presis vakansstyring er det viktigste verktøyet for å styre personalkostnadene</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakans (ledig stilling):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> En ubesatt stilling i organisasjonen som oppstår ved at en ansatt slutter, går av med pensjon, har ulønnet permisjon, eller at det opprettes en ny stillingshjemmel som ennå ikke er besatt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansfaktor (vakansreduksjon):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> En innlagt sjablongmessig reduksjon i lønnsbudsjettet (typisk </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3–5 %</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) i budsjetteringssystemer som Unit4 UBW Planlegger. Dette gjøres fordi det i praksis alltid vil ta tid (typisk </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3–6 måneder</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) å rekruttere nye ansatte, samt at det løpende oppstår naturlig avgang og permisjoner. Uten en vakansfaktor vil lønnskostnadene bli overbudsjettert dersom man forutsetter 100 % full bemanning fra 1. januar til 31. desember.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vakansstyring:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF303030"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Controllerens og ledelsens aktive oppfølging av ledige stillinger. Dette innebærer å vurdere realistisk ansettelsestidspunkt, eller vurdering av om en stilling skal holdes midlertidig vakant (f.eks. ved ansettelsesstopp / tiltak T001) for å redusere personalkostnader og gjennopprette økonomisk balanse.</t>
     </r>
   </si>
 </sst>
@@ -3956,7 +8562,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4089,6 +8695,65 @@
       <name val="Google Sans Code"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF303030"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4110,7 +8775,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4191,6 +8856,64 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6586,4 +11309,1899 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED9ED2B4-6E93-4385-A46A-6AC6A6DAF6F5}">
+  <dimension ref="A1:B78"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="34.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="29" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="30" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="29" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="29" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="29" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="42">
+      <c r="A8" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="56">
+      <c r="A9" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="56">
+      <c r="A10" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="56">
+      <c r="A11" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="33" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="22"/>
+    </row>
+    <row r="14" spans="1:2" ht="409.5">
+      <c r="A14" s="34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="409.5">
+      <c r="A15" s="34" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="409.5">
+      <c r="A16" s="34" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="402.5">
+      <c r="A17" s="34" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="29" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="29" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="29" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="33" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="22"/>
+    </row>
+    <row r="24" spans="1:1" ht="409.5">
+      <c r="A24" s="35" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="409.5">
+      <c r="A25" s="35" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="409.5">
+      <c r="A26" s="35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="30" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="29" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="29" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="29" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="33" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="29" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="22"/>
+    </row>
+    <row r="35" spans="1:1" ht="409.5">
+      <c r="A35" s="35" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="29" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="29" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="33" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="22"/>
+    </row>
+    <row r="41" spans="1:1" ht="282">
+      <c r="A41" s="35" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="409.5">
+      <c r="A42" s="35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="409.5">
+      <c r="A43" s="35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="29" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="22"/>
+    </row>
+    <row r="48" spans="1:1" ht="351">
+      <c r="A48" s="35" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="299">
+      <c r="A49" s="35" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="409.5">
+      <c r="A50" s="35" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="29" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="29" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="33" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="22"/>
+    </row>
+    <row r="56" spans="1:1" ht="409.5">
+      <c r="A56" s="35" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="409.5">
+      <c r="A57" s="35" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="180">
+      <c r="A58" s="35" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="335">
+      <c r="A59" s="36" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="409.5">
+      <c r="A60" s="36" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="29" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="29" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="22"/>
+    </row>
+    <row r="66" spans="1:1" ht="409.5">
+      <c r="A66" s="35" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="318.5">
+      <c r="A67" s="35" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="160">
+      <c r="A68" s="36" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="246.5">
+      <c r="A69" s="36" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="386.5">
+      <c r="A70" s="36" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="33" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="22"/>
+    </row>
+    <row r="74" spans="1:1" ht="370">
+      <c r="A74" s="35" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="409.5">
+      <c r="A75" s="35" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="351.5">
+      <c r="A76" s="35" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="30" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7666B8A-5B51-4D95-9849-0FFF39597F49}">
+  <dimension ref="A1:C75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="21.1796875" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" customWidth="1"/>
+    <col min="3" max="3" width="17.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="33" t="s">
+        <v>367</v>
+      </c>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="40"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="41" t="s">
+        <v>401</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="41" t="s">
+        <v>402</v>
+      </c>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="40"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="41" t="s">
+        <v>407</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="33" t="s">
+        <v>369</v>
+      </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="40"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="41" t="s">
+        <v>408</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="41" t="s">
+        <v>409</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="33" t="s">
+        <v>370</v>
+      </c>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="40"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="41" t="s">
+        <v>410</v>
+      </c>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="41" t="s">
+        <v>411</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="40"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="41" t="s">
+        <v>412</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="41" t="s">
+        <v>413</v>
+      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="39"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="39"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="43" t="s">
+        <v>377</v>
+      </c>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="43" t="s">
+        <v>379</v>
+      </c>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="39"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="40"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="44" t="s">
+        <v>382</v>
+      </c>
+      <c r="B54" s="39"/>
+      <c r="C54" s="39"/>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="44" t="s">
+        <v>415</v>
+      </c>
+      <c r="B55" s="39"/>
+      <c r="C55" s="39"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="45" t="s">
+        <v>416</v>
+      </c>
+      <c r="B56" s="39"/>
+      <c r="C56" s="39"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="41" t="s">
+        <v>383</v>
+      </c>
+      <c r="B57" s="39"/>
+      <c r="C57" s="39"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="44" t="s">
+        <v>417</v>
+      </c>
+      <c r="B58" s="39"/>
+      <c r="C58" s="39"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="44" t="s">
+        <v>418</v>
+      </c>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="44" t="s">
+        <v>419</v>
+      </c>
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="44" t="s">
+        <v>421</v>
+      </c>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="44" t="s">
+        <v>422</v>
+      </c>
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="41" t="s">
+        <v>384</v>
+      </c>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="44" t="s">
+        <v>423</v>
+      </c>
+      <c r="B65" s="39"/>
+      <c r="C65" s="39"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="44" t="s">
+        <v>424</v>
+      </c>
+      <c r="B66" s="39"/>
+      <c r="C66" s="39"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="39"/>
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="39"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="39"/>
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="33" t="s">
+        <v>385</v>
+      </c>
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+    </row>
+    <row r="71" spans="1:3" ht="56">
+      <c r="A71" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="140">
+      <c r="A72" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="B72" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="C72" s="38" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="168">
+      <c r="A73" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="B73" s="38" t="s">
+        <v>392</v>
+      </c>
+      <c r="C73" s="38" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="169">
+      <c r="A74" s="32" t="s">
+        <v>394</v>
+      </c>
+      <c r="B74" s="38" t="s">
+        <v>395</v>
+      </c>
+      <c r="C74" s="38" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="182">
+      <c r="A75" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="B75" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="C75" s="38" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D945B68-C86C-4FD2-8A17-5F8F0A6C7BC7}">
+  <dimension ref="A1:C160"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="16"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="17" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="17" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="16"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="17" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="46" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="46" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="17" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="16"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="17" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="16"/>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="17" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="17" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="16"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="17" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="17" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="17" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="19" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="19" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="19" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="19" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="16"/>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="17" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="37" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="37" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="47" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="37" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="37" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="37" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="17" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="37" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="37" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="37" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="37" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="58">
+      <c r="A71" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="145">
+      <c r="A72" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="159.5">
+      <c r="A73" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="188.5">
+      <c r="A74" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="145">
+      <c r="A75" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>398</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="12" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="16"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="37" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="37" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="17" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="37" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="48" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="48" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="48" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="16"/>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="16"/>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="16"/>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="17" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="12" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="16"/>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="17" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="12" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="16"/>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="17" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="16"/>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="17" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="17" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="17" t="s">
+        <v>505</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0EE38B-3702-46D3-9947-A53946A143EF}">
+  <dimension ref="A1:R91"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="16"/>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="17" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="17" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="17" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="17" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="17" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="17" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="R10" s="29" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="R11" s="40"/>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="R12" s="41" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="R13" s="41" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="R14" s="41" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="R15" s="39"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>517</v>
+      </c>
+      <c r="R16" s="29" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="19" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="18"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="19" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="19" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="19" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="19" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="19" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="19" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="19" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="19" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="19" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="19" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="19" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="19" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="19" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="19" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="19" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="19" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="19" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="19" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="19" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="16"/>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="17" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="17" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="17" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="47" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="47" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="16"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="17" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="17" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="17" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="17" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="17" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="16"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="17" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="17" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="16"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="17" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="17" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="16"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="17" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="17" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="17" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="16"/>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="17" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="17" t="s">
+        <v>571</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>